--- a/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68732E7-2AC1-4446-9747-263C170F0942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCB98B1-1D01-4A4D-A49D-ABE718AE2854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,12 +1289,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1335,34 +1335,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1445,63 +1424,115 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1509,39 +1540,29 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1879,1197 +1900,1197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="42">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="41" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="46">
         <v>50</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="45" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="47">
         <v>1000</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="45" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="48">
         <v>0.03</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="49">
         <v>20</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="43"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="48">
         <v>0.08</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="46" t="s">
+      <c r="A8" s="43"/>
+      <c r="B8" s="53" t="s">
         <v>331</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="50" t="s">
         <v>332</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="77">
         <f>0.36</f>
         <v>0.36</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="50" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="43"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="45" t="s">
         <v>333</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="46">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="45" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="45" t="s">
         <v>334</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="46">
         <v>7700</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="46" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="48">
         <v>0.05</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="46">
         <v>0.46</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="45" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="7" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="45" t="s">
         <v>337</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="46">
         <v>2.54</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="45" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="7" t="s">
+      <c r="A14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="45" t="s">
         <v>338</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="49">
         <v>20</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="43"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="52">
         <v>0.06</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="49" t="s">
+      <c r="A16" s="43"/>
+      <c r="B16" s="53" t="s">
         <v>255</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="54">
         <v>3.7</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="50" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="43"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="48">
         <v>0.27</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="45" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="7" t="s">
+      <c r="A18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="48">
         <v>700</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="45" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="7" t="s">
+      <c r="A19" s="43"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="48">
         <v>0.02</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="7" t="s">
+      <c r="A20" s="43"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="45" t="s">
         <v>260</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="48">
         <v>20</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="43"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="52">
         <v>0.05</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="39" t="s">
+      <c r="A22" s="43"/>
+      <c r="B22" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="46">
         <v>0.5</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="45" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="7" t="s">
+      <c r="A23" s="43"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="46">
         <v>1.75</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="45" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="7" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="46">
         <v>7000</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="45" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="7" t="s">
+      <c r="A25" s="43"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="48">
         <v>0.05</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="7" t="s">
+      <c r="A26" s="43"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="49">
         <v>15</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="36"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="7" t="s">
+      <c r="A27" s="43"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="48">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="58">
         <v>490</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="41" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="7" t="s">
+      <c r="A29" s="43"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="48">
         <v>0.01</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="7" t="s">
+      <c r="A30" s="43"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="49">
         <v>20</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="7" t="s">
+      <c r="A31" s="43"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="59">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="45" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="7" t="s">
+      <c r="A32" s="43"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="48">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="7" t="s">
+      <c r="A33" s="43"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="48">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="7" t="s">
+      <c r="A34" s="43"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="48">
         <v>0.05</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="36"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="16" t="s">
+      <c r="A35" s="43"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="52">
         <v>0</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="51" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="41" t="s">
+      <c r="A36" s="43"/>
+      <c r="B36" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="58">
         <v>2.83</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="41" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="7" t="s">
+      <c r="A37" s="43"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="48">
         <v>0.03</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="7" t="s">
+      <c r="A38" s="43"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="45" t="s">
         <v>301</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="49">
         <v>30</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="7" t="s">
+      <c r="A39" s="43"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="48">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="45" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="7" t="s">
+      <c r="A40" s="43"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="45" t="s">
         <v>303</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="48">
         <v>0.98</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="7" t="s">
+      <c r="A41" s="43"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="45" t="s">
         <v>304</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="48">
         <v>0.98</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="7" t="s">
+      <c r="A42" s="43"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="45" t="s">
         <v>305</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="48">
         <v>0.05</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="16" t="s">
+      <c r="A43" s="43"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="52">
         <v>0</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="51" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="36"/>
-      <c r="B44" s="41" t="s">
+      <c r="A44" s="43"/>
+      <c r="B44" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="54">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="50" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="7" t="s">
+      <c r="A45" s="43"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="46">
         <f>E46*4</f>
         <v>424</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="7" t="s">
+      <c r="A46" s="43"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="46">
         <v>106</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="7" t="s">
+      <c r="A47" s="43"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="48">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="45" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="7" t="s">
+      <c r="A48" s="43"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="48">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="7" t="s">
+      <c r="A49" s="43"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="48">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="7" t="s">
+      <c r="A50" s="43"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="46">
         <v>0.25</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="45" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="7" t="s">
+      <c r="A51" s="43"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="48">
         <v>0</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="45" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-      <c r="B52" s="43"/>
-      <c r="C52" s="7" t="s">
+      <c r="A52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="49">
         <v>15</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="37"/>
-      <c r="B53" s="44"/>
-      <c r="C53" s="21" t="s">
+      <c r="A53" s="62"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="65">
         <v>0.1</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="53">
+      <c r="E54" s="67">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="41" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
-      <c r="B55" s="41" t="s">
+      <c r="A55" s="43"/>
+      <c r="B55" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="54">
         <v>0.99</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="50" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="36"/>
-      <c r="B56" s="39"/>
-      <c r="C56" s="7" t="s">
+      <c r="A56" s="43"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="45" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="1">
         <v>1100</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="7" t="s">
+      <c r="A57" s="43"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="45" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="1">
         <v>17.84</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="45" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
-      <c r="C58" s="7" t="s">
+      <c r="A58" s="43"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="46">
         <v>0</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="7" t="s">
+      <c r="A59" s="43"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="49">
         <v>25</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="7" t="s">
+      <c r="A60" s="43"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="10">
+      <c r="E60" s="46">
         <v>1000000</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="45" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="16" t="s">
+      <c r="A61" s="43"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="17">
+      <c r="E61" s="52">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F61" s="16" t="s">
+      <c r="F61" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="41" t="s">
+      <c r="A62" s="43"/>
+      <c r="B62" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="54">
         <v>0.997</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="50" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="7" t="s">
+      <c r="A63" s="43"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E63" s="1">
         <v>1080</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="7" t="s">
+      <c r="A64" s="43"/>
+      <c r="B64" s="56"/>
+      <c r="C64" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="45" t="s">
         <v>52</v>
       </c>
       <c r="E64" s="1">
         <v>12.68</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="45" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="7" t="s">
+      <c r="A65" s="43"/>
+      <c r="B65" s="56"/>
+      <c r="C65" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="45" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
-      <c r="B66" s="39"/>
-      <c r="C66" s="7" t="s">
+      <c r="A66" s="43"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="49">
         <v>25</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="36"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="7" t="s">
+      <c r="A67" s="43"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="24">
+      <c r="E67" s="68">
         <v>1000000</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="45" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="21" t="s">
+      <c r="A68" s="62"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="22">
+      <c r="E68" s="65">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F68" s="21" t="s">
+      <c r="F68" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="35" t="s">
+      <c r="A69" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="26" t="s">
+      <c r="D69" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="72">
         <v>-1E-4</v>
       </c>
-      <c r="F69" s="26" t="s">
+      <c r="F69" s="71" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
-      <c r="B70" s="6" t="s">
+      <c r="A70" s="43"/>
+      <c r="B70" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="45" t="s">
         <v>283</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="48">
         <v>-1E-4</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="45" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
-      <c r="B71" s="28" t="s">
+      <c r="A71" s="43"/>
+      <c r="B71" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="30">
+      <c r="E71" s="76">
         <v>-1.5</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="75" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
-      <c r="B72" s="4" t="s">
+      <c r="A72" s="62"/>
+      <c r="B72" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="64" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="64" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="65">
         <v>-1.7</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" s="64" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3130,10 +3151,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3148,8 +3169,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="43"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3162,8 +3183,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3176,8 +3197,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="43"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3190,8 +3211,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3204,8 +3225,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3218,8 +3239,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3232,8 +3253,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="43"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3246,8 +3267,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="43"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3260,13 +3281,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="31"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="34" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3281,8 +3302,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="43"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3295,8 +3316,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3309,8 +3330,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3323,8 +3344,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3337,8 +3358,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3351,8 +3372,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3365,8 +3386,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3379,8 +3400,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="31"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3393,8 +3414,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3407,16 +3428,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="50"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="49" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="34" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3431,8 +3452,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="43"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3445,8 +3466,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="43"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3459,8 +3480,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="43"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="31"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3473,8 +3494,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="43"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3487,8 +3508,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3501,8 +3522,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="43"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3515,8 +3536,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="43"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="31"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3529,8 +3550,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="43"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3543,16 +3564,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-      <c r="B33" s="39" t="s">
+      <c r="A33" s="24"/>
+      <c r="B33" s="27" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3567,8 +3588,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="39"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3581,8 +3602,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="39"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3595,8 +3616,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="39"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3609,8 +3630,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="39"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="27"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3623,8 +3644,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="39"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3637,8 +3658,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="39"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="27"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3651,8 +3672,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="39"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="27"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3665,8 +3686,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="39"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3679,8 +3700,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="39"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="27"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3693,15 +3714,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="27"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="26" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3716,8 +3737,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-      <c r="B45" s="39"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="27"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3730,8 +3751,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
-      <c r="B46" s="39"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="27"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3744,8 +3765,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
-      <c r="B47" s="39"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="27"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3758,8 +3779,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="39"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3772,8 +3793,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-      <c r="B49" s="39"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3786,8 +3807,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="39"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3800,8 +3821,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-      <c r="B51" s="39"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3814,8 +3835,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-      <c r="B52" s="39"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="27"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3828,16 +3849,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="36"/>
-      <c r="B53" s="40"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="28"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
-      <c r="B54" s="39" t="s">
+      <c r="A54" s="24"/>
+      <c r="B54" s="27" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3852,8 +3873,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
-      <c r="B55" s="39"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="27"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3866,8 +3887,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="36"/>
-      <c r="B56" s="39"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="27"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3880,8 +3901,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="B57" s="39"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="27"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3894,8 +3915,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="27"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3908,8 +3929,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="27"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3922,8 +3943,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="27"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3936,8 +3957,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="39"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="27"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3950,8 +3971,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="39"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="27"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3964,13 +3985,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="40"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="28"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="41" t="s">
+      <c r="A64" s="24"/>
+      <c r="B64" s="29" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -3985,8 +4006,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="27"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -3999,8 +4020,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
-      <c r="B66" s="43"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="31"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -4013,8 +4034,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="36"/>
-      <c r="B67" s="43"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="31"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -4027,8 +4048,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="36"/>
-      <c r="B68" s="43"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="31"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4041,8 +4062,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="36"/>
-      <c r="B69" s="43"/>
+      <c r="A69" s="24"/>
+      <c r="B69" s="31"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4055,8 +4076,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
-      <c r="B70" s="43"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="31"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4069,8 +4090,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
-      <c r="B71" s="43"/>
+      <c r="A71" s="24"/>
+      <c r="B71" s="31"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4083,8 +4104,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
-      <c r="B72" s="43"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="31"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4097,8 +4118,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
-      <c r="B73" s="43"/>
+      <c r="A73" s="24"/>
+      <c r="B73" s="31"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4111,8 +4132,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
-      <c r="B74" s="43"/>
+      <c r="A74" s="24"/>
+      <c r="B74" s="31"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4125,18 +4146,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="37"/>
-      <c r="B75" s="44"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="21"/>
+      <c r="A75" s="25"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="45" t="s">
+      <c r="B76" s="33" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4151,8 +4172,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="36"/>
-      <c r="B77" s="43"/>
+      <c r="A77" s="24"/>
+      <c r="B77" s="31"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4165,13 +4186,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="36"/>
-      <c r="B78" s="50"/>
+      <c r="A78" s="24"/>
+      <c r="B78" s="35"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="36"/>
-      <c r="B79" s="41" t="s">
+      <c r="A79" s="24"/>
+      <c r="B79" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4186,8 +4207,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="36"/>
-      <c r="B80" s="39"/>
+      <c r="A80" s="24"/>
+      <c r="B80" s="27"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4200,8 +4221,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="36"/>
-      <c r="B81" s="39"/>
+      <c r="A81" s="24"/>
+      <c r="B81" s="27"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4214,8 +4235,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="36"/>
-      <c r="B82" s="39"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="27"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4228,8 +4249,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="36"/>
-      <c r="B83" s="39"/>
+      <c r="A83" s="24"/>
+      <c r="B83" s="27"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4242,8 +4263,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="36"/>
-      <c r="B84" s="39"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="27"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4256,8 +4277,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="36"/>
-      <c r="B85" s="39"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="27"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4270,8 +4291,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="36"/>
-      <c r="B86" s="39"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="27"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4284,8 +4305,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="36"/>
-      <c r="B87" s="39"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="27"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4298,12 +4319,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="36"/>
-      <c r="B88" s="40"/>
+      <c r="A88" s="24"/>
+      <c r="B88" s="28"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="36"/>
-      <c r="B89" s="41" t="s">
+      <c r="A89" s="24"/>
+      <c r="B89" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4318,8 +4339,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="36"/>
-      <c r="B90" s="39"/>
+      <c r="A90" s="24"/>
+      <c r="B90" s="27"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4332,8 +4353,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="36"/>
-      <c r="B91" s="39"/>
+      <c r="A91" s="24"/>
+      <c r="B91" s="27"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4346,8 +4367,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="36"/>
-      <c r="B92" s="39"/>
+      <c r="A92" s="24"/>
+      <c r="B92" s="27"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4360,8 +4381,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="36"/>
-      <c r="B93" s="39"/>
+      <c r="A93" s="24"/>
+      <c r="B93" s="27"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4374,36 +4395,36 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="36"/>
-      <c r="B94" s="39"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="27"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E94" s="24"/>
+      <c r="E94" s="22"/>
       <c r="F94" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="36"/>
-      <c r="B95" s="39"/>
+      <c r="A95" s="24"/>
+      <c r="B95" s="27"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E95" s="24"/>
+      <c r="E95" s="22"/>
       <c r="F95" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="36"/>
-      <c r="B96" s="39"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="27"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4416,8 +4437,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="36"/>
-      <c r="B97" s="39"/>
+      <c r="A97" s="24"/>
+      <c r="B97" s="27"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4430,14 +4451,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="37"/>
-      <c r="B98" s="42"/>
+      <c r="A98" s="25"/>
+      <c r="B98" s="30"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="35" t="s">
+      <c r="A99" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="45" t="s">
+      <c r="B99" s="33" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4452,8 +4473,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="36"/>
-      <c r="B100" s="43"/>
+      <c r="A100" s="24"/>
+      <c r="B100" s="31"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4466,8 +4487,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="36"/>
-      <c r="B101" s="43"/>
+      <c r="A101" s="24"/>
+      <c r="B101" s="31"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4480,16 +4501,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="36"/>
-      <c r="B102" s="50"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="35"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="36"/>
-      <c r="B103" s="49" t="s">
+      <c r="A103" s="24"/>
+      <c r="B103" s="34" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4504,8 +4525,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="36"/>
-      <c r="B104" s="43"/>
+      <c r="A104" s="24"/>
+      <c r="B104" s="31"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4518,8 +4539,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="36"/>
-      <c r="B105" s="43"/>
+      <c r="A105" s="24"/>
+      <c r="B105" s="31"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4532,13 +4553,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="36"/>
-      <c r="B106" s="50"/>
+      <c r="A106" s="24"/>
+      <c r="B106" s="35"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="36"/>
-      <c r="B107" s="49" t="s">
+      <c r="A107" s="24"/>
+      <c r="B107" s="34" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4553,8 +4574,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="36"/>
-      <c r="B108" s="43"/>
+      <c r="A108" s="24"/>
+      <c r="B108" s="31"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4567,16 +4588,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="36"/>
-      <c r="B109" s="50"/>
+      <c r="A109" s="24"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
-      <c r="B110" s="49" t="s">
+      <c r="A110" s="24"/>
+      <c r="B110" s="34" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4591,8 +4612,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
-      <c r="B111" s="43"/>
+      <c r="A111" s="24"/>
+      <c r="B111" s="31"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4605,18 +4626,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="37"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="21"/>
+      <c r="A112" s="25"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="20"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="21"/>
+      <c r="F112" s="20"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="35" t="s">
+      <c r="A113" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="45" t="s">
+      <c r="B113" s="33" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4631,8 +4652,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="52"/>
-      <c r="B114" s="43"/>
+      <c r="A114" s="24"/>
+      <c r="B114" s="31"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4644,16 +4665,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="52"/>
-      <c r="B115" s="50"/>
+      <c r="A115" s="24"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="52"/>
-      <c r="B116" s="49" t="s">
+      <c r="A116" s="24"/>
+      <c r="B116" s="34" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4667,8 +4688,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="52"/>
-      <c r="B117" s="43"/>
+      <c r="A117" s="24"/>
+      <c r="B117" s="31"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4680,8 +4701,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="52"/>
-      <c r="B118" s="43"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="31"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4693,8 +4714,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="52"/>
-      <c r="B119" s="43"/>
+      <c r="A119" s="24"/>
+      <c r="B119" s="31"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4706,8 +4727,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="52"/>
-      <c r="B120" s="43"/>
+      <c r="A120" s="24"/>
+      <c r="B120" s="31"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4719,8 +4740,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="52"/>
-      <c r="B121" s="43"/>
+      <c r="A121" s="24"/>
+      <c r="B121" s="31"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4732,12 +4753,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="52"/>
-      <c r="B122" s="43"/>
+      <c r="A122" s="24"/>
+      <c r="B122" s="31"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="52"/>
-      <c r="B123" s="49" t="s">
+      <c r="A123" s="24"/>
+      <c r="B123" s="34" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4752,8 +4773,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="52"/>
-      <c r="B124" s="43"/>
+      <c r="A124" s="24"/>
+      <c r="B124" s="31"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4765,8 +4786,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="52"/>
-      <c r="B125" s="43"/>
+      <c r="A125" s="24"/>
+      <c r="B125" s="31"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4778,8 +4799,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="52"/>
-      <c r="B126" s="43"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="31"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4791,8 +4812,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="52"/>
-      <c r="B127" s="43"/>
+      <c r="A127" s="24"/>
+      <c r="B127" s="31"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4804,8 +4825,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="52"/>
-      <c r="B128" s="43"/>
+      <c r="A128" s="24"/>
+      <c r="B128" s="31"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4817,8 +4838,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="52"/>
-      <c r="B129" s="43"/>
+      <c r="A129" s="24"/>
+      <c r="B129" s="31"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4830,8 +4851,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="52"/>
-      <c r="B130" s="43"/>
+      <c r="A130" s="24"/>
+      <c r="B130" s="31"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4843,8 +4864,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="52"/>
-      <c r="B131" s="43"/>
+      <c r="A131" s="24"/>
+      <c r="B131" s="31"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4856,8 +4877,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="52"/>
-      <c r="B132" s="43"/>
+      <c r="A132" s="24"/>
+      <c r="B132" s="31"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4869,8 +4890,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="52"/>
-      <c r="B133" s="43"/>
+      <c r="A133" s="24"/>
+      <c r="B133" s="31"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4882,8 +4903,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="52"/>
-      <c r="B134" s="43"/>
+      <c r="A134" s="24"/>
+      <c r="B134" s="31"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4895,12 +4916,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="52"/>
-      <c r="B135" s="43"/>
+      <c r="A135" s="24"/>
+      <c r="B135" s="31"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="52"/>
-      <c r="B136" s="49" t="s">
+      <c r="A136" s="24"/>
+      <c r="B136" s="34" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4915,8 +4936,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="52"/>
-      <c r="B137" s="51"/>
+      <c r="A137" s="24"/>
+      <c r="B137" s="31"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4928,8 +4949,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="52"/>
-      <c r="B138" s="51"/>
+      <c r="A138" s="24"/>
+      <c r="B138" s="31"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4941,8 +4962,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="52"/>
-      <c r="B139" s="51"/>
+      <c r="A139" s="24"/>
+      <c r="B139" s="31"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4954,8 +4975,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="52"/>
-      <c r="B140" s="51"/>
+      <c r="A140" s="24"/>
+      <c r="B140" s="31"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4967,12 +4988,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="52"/>
-      <c r="B141" s="51"/>
+      <c r="A141" s="24"/>
+      <c r="B141" s="31"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="52"/>
-      <c r="B142" s="49" t="s">
+      <c r="A142" s="24"/>
+      <c r="B142" s="34" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -4987,29 +5008,20 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="52"/>
-      <c r="B143" s="51"/>
-      <c r="C143" s="31" t="s">
+      <c r="A143" s="24"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D143" s="31" t="s">
+      <c r="D143" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E143" s="31"/>
-      <c r="F143" s="31" t="s">
+      <c r="F143" s="7" t="s">
         <v>362</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5026,6 +5038,14 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCB98B1-1D01-4A4D-A49D-ABE718AE2854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B3F404-4EE8-465D-85FE-0A98AA77E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,10 +1289,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1424,115 +1424,82 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1540,29 +1507,62 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1900,1197 +1900,1197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="27">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="29">
         <v>50</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="28" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="30">
         <v>1000</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="28" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="43"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="31">
         <v>0.03</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="43"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="32">
         <v>20</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="31">
         <v>0.08</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="43"/>
-      <c r="B8" s="53" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="63" t="s">
         <v>331</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="33" t="s">
         <v>332</v>
       </c>
-      <c r="E8" s="77">
+      <c r="E8" s="51">
         <f>0.36</f>
         <v>0.36</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="33" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="43"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="29">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="43"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="28" t="s">
         <v>334</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="29">
         <v>7700</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="29" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="28" t="s">
         <v>335</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="31">
         <v>0.05</v>
       </c>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="29">
         <v>0.46</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="28" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="45" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="29">
         <v>2.54</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="28" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="45" t="s">
+      <c r="A14" s="53"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="28" t="s">
         <v>338</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="32">
         <v>20</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="51" t="s">
+      <c r="A15" s="53"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="35">
         <v>0.06</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F15" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="53" t="s">
+      <c r="A16" s="53"/>
+      <c r="B16" s="63" t="s">
         <v>255</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="36">
         <v>3.7</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45" t="s">
+      <c r="A17" s="53"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="31">
         <v>0.27</v>
       </c>
-      <c r="F17" s="45" t="s">
+      <c r="F17" s="28" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="31">
         <v>700</v>
       </c>
-      <c r="F18" s="45" t="s">
+      <c r="F18" s="28" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="31">
         <v>0.02</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45" t="s">
+      <c r="A20" s="53"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="31">
         <v>20</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="43"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="51" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="35">
         <v>0.05</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="43"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="29">
         <v>0.5</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="28" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="43"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="56"/>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="29">
         <v>1.75</v>
       </c>
-      <c r="F23" s="45" t="s">
+      <c r="F23" s="28" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="43"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="56"/>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="29">
         <v>7000</v>
       </c>
-      <c r="F24" s="45" t="s">
+      <c r="F24" s="28" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="43"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="56"/>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="31">
         <v>0.05</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="43"/>
+      <c r="A26" s="53"/>
       <c r="B26" s="56"/>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="32">
         <v>15</v>
       </c>
-      <c r="F26" s="45" t="s">
+      <c r="F26" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="43"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="56"/>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="41" t="s">
+      <c r="D28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="58">
+      <c r="E28" s="37">
         <v>490</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="26" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="43"/>
+      <c r="A29" s="53"/>
       <c r="B29" s="56"/>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="48">
+      <c r="E29" s="31">
         <v>0.01</v>
       </c>
-      <c r="F29" s="45" t="s">
+      <c r="F29" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="43"/>
+      <c r="A30" s="53"/>
       <c r="B30" s="56"/>
-      <c r="C30" s="45" t="s">
+      <c r="C30" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="32">
         <v>20</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="43"/>
+      <c r="A31" s="53"/>
       <c r="B31" s="56"/>
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="59">
+      <c r="E31" s="38">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F31" s="45" t="s">
+      <c r="F31" s="28" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="43"/>
+      <c r="A32" s="53"/>
       <c r="B32" s="56"/>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="48">
+      <c r="E32" s="31">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="43"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="56"/>
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="31">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F33" s="45" t="s">
+      <c r="F33" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="43"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="56"/>
-      <c r="C34" s="45" t="s">
+      <c r="C34" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="48">
+      <c r="E34" s="31">
         <v>0.05</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="43"/>
-      <c r="B35" s="60"/>
-      <c r="C35" s="51" t="s">
+      <c r="A35" s="53"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="35">
         <v>0</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="34" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="43"/>
-      <c r="B36" s="61" t="s">
+      <c r="A36" s="53"/>
+      <c r="B36" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="E36" s="58">
+      <c r="E36" s="37">
         <v>2.83</v>
       </c>
-      <c r="F36" s="41" t="s">
+      <c r="F36" s="26" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="43"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="56"/>
-      <c r="C37" s="45" t="s">
+      <c r="C37" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="E37" s="48">
+      <c r="E37" s="31">
         <v>0.03</v>
       </c>
-      <c r="F37" s="45" t="s">
+      <c r="F37" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="43"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="56"/>
-      <c r="C38" s="45" t="s">
+      <c r="C38" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="32">
         <v>30</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="43"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="56"/>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="E39" s="48">
+      <c r="E39" s="31">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="28" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="43"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="56"/>
-      <c r="C40" s="45" t="s">
+      <c r="C40" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="D40" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="E40" s="48">
+      <c r="E40" s="31">
         <v>0.98</v>
       </c>
-      <c r="F40" s="45" t="s">
+      <c r="F40" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="43"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="56"/>
-      <c r="C41" s="45" t="s">
+      <c r="C41" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="E41" s="48">
+      <c r="E41" s="31">
         <v>0.98</v>
       </c>
-      <c r="F41" s="45" t="s">
+      <c r="F41" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="43"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="56"/>
-      <c r="C42" s="45" t="s">
+      <c r="C42" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="E42" s="48">
+      <c r="E42" s="31">
         <v>0.05</v>
       </c>
-      <c r="F42" s="45" t="s">
+      <c r="F42" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="43"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="56"/>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="51" t="s">
+      <c r="D43" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="E43" s="52">
+      <c r="E43" s="35">
         <v>0</v>
       </c>
-      <c r="F43" s="51" t="s">
+      <c r="F43" s="34" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="43"/>
-      <c r="B44" s="61" t="s">
+      <c r="A44" s="53"/>
+      <c r="B44" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="54">
+      <c r="E44" s="36">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F44" s="50" t="s">
+      <c r="F44" s="33" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="43"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="45" t="s">
+      <c r="A45" s="53"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="46">
+      <c r="E45" s="29">
         <f>E46*4</f>
         <v>424</v>
       </c>
-      <c r="F45" s="45" t="s">
+      <c r="F45" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="43"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="45" t="s">
+      <c r="A46" s="53"/>
+      <c r="B46" s="60"/>
+      <c r="C46" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="45" t="s">
+      <c r="D46" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="46">
+      <c r="E46" s="29">
         <v>106</v>
       </c>
-      <c r="F46" s="45" t="s">
+      <c r="F46" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="43"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="45" t="s">
+      <c r="A47" s="53"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="48">
+      <c r="E47" s="31">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F47" s="45" t="s">
+      <c r="F47" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="43"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="45" t="s">
+      <c r="A48" s="53"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="45" t="s">
+      <c r="D48" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="48">
+      <c r="E48" s="31">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F48" s="45" t="s">
+      <c r="F48" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="43"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="45" t="s">
+      <c r="A49" s="53"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D49" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="31">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F49" s="45" t="s">
+      <c r="F49" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="43"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="45" t="s">
+      <c r="A50" s="53"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="45" t="s">
+      <c r="D50" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="46">
+      <c r="E50" s="29">
         <v>0.25</v>
       </c>
-      <c r="F50" s="45" t="s">
+      <c r="F50" s="28" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="43"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="45" t="s">
+      <c r="A51" s="53"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="45" t="s">
+      <c r="D51" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="48">
+      <c r="E51" s="31">
         <v>0</v>
       </c>
-      <c r="F51" s="45" t="s">
+      <c r="F51" s="28" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="43"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="45" t="s">
+      <c r="A52" s="53"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="45" t="s">
+      <c r="D52" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="49">
+      <c r="E52" s="32">
         <v>15</v>
       </c>
-      <c r="F52" s="45" t="s">
+      <c r="F52" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="62"/>
-      <c r="B53" s="63"/>
-      <c r="C53" s="64" t="s">
+      <c r="A53" s="54"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="64" t="s">
+      <c r="D53" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="65">
+      <c r="E53" s="40">
         <v>0.1</v>
       </c>
-      <c r="F53" s="64" t="s">
+      <c r="F53" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="66" t="s">
+      <c r="B54" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="41" t="s">
+      <c r="C54" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="D54" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="67">
+      <c r="E54" s="42">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="F54" s="41" t="s">
+      <c r="F54" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="43"/>
-      <c r="B55" s="61" t="s">
+      <c r="A55" s="53"/>
+      <c r="B55" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="50" t="s">
+      <c r="D55" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="54">
+      <c r="E55" s="36">
         <v>0.99</v>
       </c>
-      <c r="F55" s="50" t="s">
+      <c r="F55" s="33" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="43"/>
+      <c r="A56" s="53"/>
       <c r="B56" s="56"/>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="28" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="1">
         <v>1100</v>
       </c>
-      <c r="F56" s="45" t="s">
+      <c r="F56" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="43"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="56"/>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="28" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="1">
         <v>17.84</v>
       </c>
-      <c r="F57" s="45" t="s">
+      <c r="F57" s="28" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
+      <c r="A58" s="53"/>
       <c r="B58" s="56"/>
-      <c r="C58" s="45" t="s">
+      <c r="C58" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="46">
+      <c r="E58" s="29">
         <v>0</v>
       </c>
-      <c r="F58" s="45" t="s">
+      <c r="F58" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="43"/>
+      <c r="A59" s="53"/>
       <c r="B59" s="56"/>
-      <c r="C59" s="45" t="s">
+      <c r="C59" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="45" t="s">
+      <c r="D59" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="49">
+      <c r="E59" s="32">
         <v>25</v>
       </c>
-      <c r="F59" s="45" t="s">
+      <c r="F59" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="43"/>
+      <c r="A60" s="53"/>
       <c r="B60" s="56"/>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="46">
+      <c r="E60" s="29">
         <v>1000000</v>
       </c>
-      <c r="F60" s="45" t="s">
+      <c r="F60" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="43"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="51" t="s">
+      <c r="A61" s="53"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="51" t="s">
+      <c r="D61" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="52">
+      <c r="E61" s="35">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F61" s="51" t="s">
+      <c r="F61" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="43"/>
-      <c r="B62" s="61" t="s">
+      <c r="A62" s="53"/>
+      <c r="B62" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="50" t="s">
+      <c r="D62" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="54">
+      <c r="E62" s="36">
         <v>0.997</v>
       </c>
-      <c r="F62" s="50" t="s">
+      <c r="F62" s="33" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="43"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="56"/>
-      <c r="C63" s="45" t="s">
+      <c r="C63" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="28" t="s">
         <v>48</v>
       </c>
       <c r="E63" s="1">
         <v>1080</v>
       </c>
-      <c r="F63" s="45" t="s">
+      <c r="F63" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="43"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="56"/>
-      <c r="C64" s="45" t="s">
+      <c r="C64" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="45" t="s">
+      <c r="D64" s="28" t="s">
         <v>52</v>
       </c>
       <c r="E64" s="1">
         <v>12.68</v>
       </c>
-      <c r="F64" s="45" t="s">
+      <c r="F64" s="28" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="43"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="56"/>
-      <c r="C65" s="45" t="s">
+      <c r="C65" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="45" t="s">
+      <c r="D65" s="28" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F65" s="45" t="s">
+      <c r="F65" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="43"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="56"/>
-      <c r="C66" s="45" t="s">
+      <c r="C66" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="45" t="s">
+      <c r="D66" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="49">
+      <c r="E66" s="32">
         <v>25</v>
       </c>
-      <c r="F66" s="45" t="s">
+      <c r="F66" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="43"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="56"/>
-      <c r="C67" s="45" t="s">
+      <c r="C67" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="45" t="s">
+      <c r="D67" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="68">
+      <c r="E67" s="43">
         <v>1000000</v>
       </c>
-      <c r="F67" s="45" t="s">
+      <c r="F67" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="62"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="64" t="s">
+      <c r="A68" s="54"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="64" t="s">
+      <c r="D68" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="65">
+      <c r="E68" s="40">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F68" s="64" t="s">
+      <c r="F68" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="39" t="s">
+      <c r="A69" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="70" t="s">
+      <c r="B69" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="71" t="s">
+      <c r="C69" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="71" t="s">
+      <c r="D69" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="72">
-        <v>-1E-4</v>
-      </c>
-      <c r="F69" s="71" t="s">
+      <c r="E69" s="46">
+        <v>0</v>
+      </c>
+      <c r="F69" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="43"/>
-      <c r="B70" s="73" t="s">
+      <c r="A70" s="53"/>
+      <c r="B70" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="45" t="s">
+      <c r="C70" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="45" t="s">
+      <c r="D70" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="E70" s="48">
-        <v>-1E-4</v>
-      </c>
-      <c r="F70" s="45" t="s">
+      <c r="E70" s="31">
+        <v>0</v>
+      </c>
+      <c r="F70" s="28" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="43"/>
-      <c r="B71" s="74" t="s">
+      <c r="A71" s="53"/>
+      <c r="B71" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="75" t="s">
+      <c r="C71" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="75" t="s">
+      <c r="D71" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="76">
+      <c r="E71" s="50">
         <v>-1.5</v>
       </c>
-      <c r="F71" s="75" t="s">
+      <c r="F71" s="49" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="62"/>
-      <c r="B72" s="37" t="s">
+      <c r="A72" s="54"/>
+      <c r="B72" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="64" t="s">
+      <c r="C72" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="64" t="s">
+      <c r="D72" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="65">
+      <c r="E72" s="40">
         <v>-1.7</v>
       </c>
-      <c r="F72" s="64" t="s">
+      <c r="F72" s="39" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3151,10 +3151,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3169,8 +3169,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="66"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3183,8 +3183,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="66"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3197,8 +3197,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="66"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3211,8 +3211,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="66"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3225,8 +3225,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3239,8 +3239,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="31"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="66"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3253,8 +3253,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="66"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3267,8 +3267,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="31"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3281,13 +3281,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="66"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="68"/>
+      <c r="B12" s="65" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3302,8 +3302,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3316,8 +3316,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3330,8 +3330,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="31"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3344,8 +3344,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="68"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3358,8 +3358,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="68"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3372,8 +3372,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3386,8 +3386,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3400,8 +3400,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="66"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3414,8 +3414,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="68"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3428,16 +3428,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="24"/>
-      <c r="B22" s="35"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="70"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="68"/>
+      <c r="B23" s="65" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3452,8 +3452,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
-      <c r="B24" s="31"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3466,8 +3466,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3480,8 +3480,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
-      <c r="B26" s="31"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="66"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3494,8 +3494,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="31"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="66"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3508,8 +3508,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
-      <c r="B28" s="31"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="66"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3522,8 +3522,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="66"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3536,8 +3536,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="66"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3550,8 +3550,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="24"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="68"/>
+      <c r="B31" s="66"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3564,16 +3564,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="24"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="70"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="24"/>
-      <c r="B33" s="27" t="s">
+      <c r="A33" s="68"/>
+      <c r="B33" s="71" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3588,8 +3588,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="24"/>
-      <c r="B34" s="27"/>
+      <c r="A34" s="68"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3602,8 +3602,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
-      <c r="B35" s="27"/>
+      <c r="A35" s="68"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3616,8 +3616,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="24"/>
-      <c r="B36" s="27"/>
+      <c r="A36" s="68"/>
+      <c r="B36" s="71"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3630,8 +3630,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="24"/>
-      <c r="B37" s="27"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="71"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3644,8 +3644,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="24"/>
-      <c r="B38" s="27"/>
+      <c r="A38" s="68"/>
+      <c r="B38" s="71"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3658,8 +3658,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="24"/>
-      <c r="B39" s="27"/>
+      <c r="A39" s="68"/>
+      <c r="B39" s="71"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3672,8 +3672,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="24"/>
-      <c r="B40" s="27"/>
+      <c r="A40" s="68"/>
+      <c r="B40" s="71"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3686,8 +3686,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="24"/>
-      <c r="B41" s="27"/>
+      <c r="A41" s="68"/>
+      <c r="B41" s="71"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3700,8 +3700,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="24"/>
-      <c r="B42" s="27"/>
+      <c r="A42" s="68"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3714,15 +3714,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="24"/>
-      <c r="B43" s="27"/>
+      <c r="A43" s="68"/>
+      <c r="B43" s="71"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="75" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3737,8 +3737,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="24"/>
-      <c r="B45" s="27"/>
+      <c r="A45" s="68"/>
+      <c r="B45" s="71"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3751,8 +3751,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="24"/>
-      <c r="B46" s="27"/>
+      <c r="A46" s="68"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3765,8 +3765,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="24"/>
-      <c r="B47" s="27"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="71"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3779,8 +3779,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="24"/>
-      <c r="B48" s="27"/>
+      <c r="A48" s="68"/>
+      <c r="B48" s="71"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3793,8 +3793,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="24"/>
-      <c r="B49" s="27"/>
+      <c r="A49" s="68"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3807,8 +3807,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="24"/>
-      <c r="B50" s="27"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="71"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3821,8 +3821,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="24"/>
-      <c r="B51" s="27"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="71"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3835,8 +3835,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
-      <c r="B52" s="27"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="71"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3849,16 +3849,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="24"/>
-      <c r="B53" s="28"/>
+      <c r="A53" s="68"/>
+      <c r="B53" s="76"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="24"/>
-      <c r="B54" s="27" t="s">
+      <c r="A54" s="68"/>
+      <c r="B54" s="71" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3873,8 +3873,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="24"/>
-      <c r="B55" s="27"/>
+      <c r="A55" s="68"/>
+      <c r="B55" s="71"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3887,8 +3887,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="24"/>
-      <c r="B56" s="27"/>
+      <c r="A56" s="68"/>
+      <c r="B56" s="71"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3901,8 +3901,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="24"/>
-      <c r="B57" s="27"/>
+      <c r="A57" s="68"/>
+      <c r="B57" s="71"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3915,8 +3915,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="24"/>
-      <c r="B58" s="27"/>
+      <c r="A58" s="68"/>
+      <c r="B58" s="71"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3929,8 +3929,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="24"/>
-      <c r="B59" s="27"/>
+      <c r="A59" s="68"/>
+      <c r="B59" s="71"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3943,8 +3943,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="24"/>
-      <c r="B60" s="27"/>
+      <c r="A60" s="68"/>
+      <c r="B60" s="71"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3957,8 +3957,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="24"/>
-      <c r="B61" s="27"/>
+      <c r="A61" s="68"/>
+      <c r="B61" s="71"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3971,8 +3971,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="24"/>
-      <c r="B62" s="27"/>
+      <c r="A62" s="68"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3985,13 +3985,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="24"/>
-      <c r="B63" s="28"/>
+      <c r="A63" s="68"/>
+      <c r="B63" s="76"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="24"/>
-      <c r="B64" s="29" t="s">
+      <c r="A64" s="68"/>
+      <c r="B64" s="73" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -4006,8 +4006,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="24"/>
-      <c r="B65" s="27"/>
+      <c r="A65" s="68"/>
+      <c r="B65" s="71"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -4020,8 +4020,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="24"/>
-      <c r="B66" s="31"/>
+      <c r="A66" s="68"/>
+      <c r="B66" s="66"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -4034,8 +4034,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="24"/>
-      <c r="B67" s="31"/>
+      <c r="A67" s="68"/>
+      <c r="B67" s="66"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -4048,8 +4048,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="24"/>
-      <c r="B68" s="31"/>
+      <c r="A68" s="68"/>
+      <c r="B68" s="66"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4062,8 +4062,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="24"/>
-      <c r="B69" s="31"/>
+      <c r="A69" s="68"/>
+      <c r="B69" s="66"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4076,8 +4076,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="24"/>
-      <c r="B70" s="31"/>
+      <c r="A70" s="68"/>
+      <c r="B70" s="66"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4090,8 +4090,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="24"/>
-      <c r="B71" s="31"/>
+      <c r="A71" s="68"/>
+      <c r="B71" s="66"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4104,8 +4104,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="24"/>
-      <c r="B72" s="31"/>
+      <c r="A72" s="68"/>
+      <c r="B72" s="66"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4118,8 +4118,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="24"/>
-      <c r="B73" s="31"/>
+      <c r="A73" s="68"/>
+      <c r="B73" s="66"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4132,8 +4132,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="24"/>
-      <c r="B74" s="31"/>
+      <c r="A74" s="68"/>
+      <c r="B74" s="66"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4146,18 +4146,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="25"/>
-      <c r="B75" s="32"/>
+      <c r="A75" s="72"/>
+      <c r="B75" s="74"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="21"/>
       <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="69" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4172,8 +4172,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="24"/>
-      <c r="B77" s="31"/>
+      <c r="A77" s="68"/>
+      <c r="B77" s="66"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4186,13 +4186,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="24"/>
-      <c r="B78" s="35"/>
+      <c r="A78" s="68"/>
+      <c r="B78" s="70"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="24"/>
-      <c r="B79" s="29" t="s">
+      <c r="A79" s="68"/>
+      <c r="B79" s="73" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4207,8 +4207,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="24"/>
-      <c r="B80" s="27"/>
+      <c r="A80" s="68"/>
+      <c r="B80" s="71"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4221,8 +4221,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="24"/>
-      <c r="B81" s="27"/>
+      <c r="A81" s="68"/>
+      <c r="B81" s="71"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4235,8 +4235,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="24"/>
-      <c r="B82" s="27"/>
+      <c r="A82" s="68"/>
+      <c r="B82" s="71"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4249,8 +4249,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="24"/>
-      <c r="B83" s="27"/>
+      <c r="A83" s="68"/>
+      <c r="B83" s="71"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4263,8 +4263,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="24"/>
-      <c r="B84" s="27"/>
+      <c r="A84" s="68"/>
+      <c r="B84" s="71"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4277,8 +4277,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="24"/>
-      <c r="B85" s="27"/>
+      <c r="A85" s="68"/>
+      <c r="B85" s="71"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4291,8 +4291,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="24"/>
-      <c r="B86" s="27"/>
+      <c r="A86" s="68"/>
+      <c r="B86" s="71"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4305,8 +4305,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="24"/>
-      <c r="B87" s="27"/>
+      <c r="A87" s="68"/>
+      <c r="B87" s="71"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4319,12 +4319,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="24"/>
-      <c r="B88" s="28"/>
+      <c r="A88" s="68"/>
+      <c r="B88" s="76"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="24"/>
-      <c r="B89" s="29" t="s">
+      <c r="A89" s="68"/>
+      <c r="B89" s="73" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4339,8 +4339,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="24"/>
-      <c r="B90" s="27"/>
+      <c r="A90" s="68"/>
+      <c r="B90" s="71"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4353,8 +4353,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="24"/>
-      <c r="B91" s="27"/>
+      <c r="A91" s="68"/>
+      <c r="B91" s="71"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4367,8 +4367,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="24"/>
-      <c r="B92" s="27"/>
+      <c r="A92" s="68"/>
+      <c r="B92" s="71"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4381,8 +4381,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="24"/>
-      <c r="B93" s="27"/>
+      <c r="A93" s="68"/>
+      <c r="B93" s="71"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4395,8 +4395,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="24"/>
-      <c r="B94" s="27"/>
+      <c r="A94" s="68"/>
+      <c r="B94" s="71"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4409,8 +4409,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="24"/>
-      <c r="B95" s="27"/>
+      <c r="A95" s="68"/>
+      <c r="B95" s="71"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4423,8 +4423,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="24"/>
-      <c r="B96" s="27"/>
+      <c r="A96" s="68"/>
+      <c r="B96" s="71"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4437,8 +4437,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="24"/>
-      <c r="B97" s="27"/>
+      <c r="A97" s="68"/>
+      <c r="B97" s="71"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4451,14 +4451,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="25"/>
-      <c r="B98" s="30"/>
+      <c r="A98" s="72"/>
+      <c r="B98" s="77"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="23" t="s">
+      <c r="A99" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="33" t="s">
+      <c r="B99" s="69" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4473,8 +4473,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="24"/>
-      <c r="B100" s="31"/>
+      <c r="A100" s="68"/>
+      <c r="B100" s="66"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4487,8 +4487,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="24"/>
-      <c r="B101" s="31"/>
+      <c r="A101" s="68"/>
+      <c r="B101" s="66"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4501,16 +4501,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="24"/>
-      <c r="B102" s="35"/>
+      <c r="A102" s="68"/>
+      <c r="B102" s="70"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="24"/>
-      <c r="B103" s="34" t="s">
+      <c r="A103" s="68"/>
+      <c r="B103" s="65" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4525,8 +4525,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="24"/>
-      <c r="B104" s="31"/>
+      <c r="A104" s="68"/>
+      <c r="B104" s="66"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4539,8 +4539,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="24"/>
-      <c r="B105" s="31"/>
+      <c r="A105" s="68"/>
+      <c r="B105" s="66"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="24"/>
-      <c r="B106" s="35"/>
+      <c r="A106" s="68"/>
+      <c r="B106" s="70"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="24"/>
-      <c r="B107" s="34" t="s">
+      <c r="A107" s="68"/>
+      <c r="B107" s="65" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4574,8 +4574,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="24"/>
-      <c r="B108" s="31"/>
+      <c r="A108" s="68"/>
+      <c r="B108" s="66"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4588,16 +4588,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="24"/>
-      <c r="B109" s="35"/>
+      <c r="A109" s="68"/>
+      <c r="B109" s="70"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="24"/>
-      <c r="B110" s="34" t="s">
+      <c r="A110" s="68"/>
+      <c r="B110" s="65" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4612,8 +4612,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="24"/>
-      <c r="B111" s="31"/>
+      <c r="A111" s="68"/>
+      <c r="B111" s="66"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4626,18 +4626,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="25"/>
-      <c r="B112" s="32"/>
+      <c r="A112" s="72"/>
+      <c r="B112" s="74"/>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="21"/>
       <c r="F112" s="20"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="23" t="s">
+      <c r="A113" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="69" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4652,8 +4652,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="24"/>
-      <c r="B114" s="31"/>
+      <c r="A114" s="68"/>
+      <c r="B114" s="66"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4665,16 +4665,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="24"/>
-      <c r="B115" s="35"/>
+      <c r="A115" s="68"/>
+      <c r="B115" s="70"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="24"/>
-      <c r="B116" s="34" t="s">
+      <c r="A116" s="68"/>
+      <c r="B116" s="65" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4688,8 +4688,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="24"/>
-      <c r="B117" s="31"/>
+      <c r="A117" s="68"/>
+      <c r="B117" s="66"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4701,8 +4701,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="24"/>
-      <c r="B118" s="31"/>
+      <c r="A118" s="68"/>
+      <c r="B118" s="66"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4714,8 +4714,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="24"/>
-      <c r="B119" s="31"/>
+      <c r="A119" s="68"/>
+      <c r="B119" s="66"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4727,8 +4727,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="24"/>
-      <c r="B120" s="31"/>
+      <c r="A120" s="68"/>
+      <c r="B120" s="66"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4740,8 +4740,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="24"/>
-      <c r="B121" s="31"/>
+      <c r="A121" s="68"/>
+      <c r="B121" s="66"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4753,12 +4753,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="24"/>
-      <c r="B122" s="31"/>
+      <c r="A122" s="68"/>
+      <c r="B122" s="66"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="24"/>
-      <c r="B123" s="34" t="s">
+      <c r="A123" s="68"/>
+      <c r="B123" s="65" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4773,8 +4773,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="24"/>
-      <c r="B124" s="31"/>
+      <c r="A124" s="68"/>
+      <c r="B124" s="66"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4786,8 +4786,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="24"/>
-      <c r="B125" s="31"/>
+      <c r="A125" s="68"/>
+      <c r="B125" s="66"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4799,8 +4799,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="24"/>
-      <c r="B126" s="31"/>
+      <c r="A126" s="68"/>
+      <c r="B126" s="66"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4812,8 +4812,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="24"/>
-      <c r="B127" s="31"/>
+      <c r="A127" s="68"/>
+      <c r="B127" s="66"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4825,8 +4825,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="24"/>
-      <c r="B128" s="31"/>
+      <c r="A128" s="68"/>
+      <c r="B128" s="66"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4838,8 +4838,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="24"/>
-      <c r="B129" s="31"/>
+      <c r="A129" s="68"/>
+      <c r="B129" s="66"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4851,8 +4851,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="24"/>
-      <c r="B130" s="31"/>
+      <c r="A130" s="68"/>
+      <c r="B130" s="66"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4864,8 +4864,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="24"/>
-      <c r="B131" s="31"/>
+      <c r="A131" s="68"/>
+      <c r="B131" s="66"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4877,8 +4877,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="24"/>
-      <c r="B132" s="31"/>
+      <c r="A132" s="68"/>
+      <c r="B132" s="66"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4890,8 +4890,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="24"/>
-      <c r="B133" s="31"/>
+      <c r="A133" s="68"/>
+      <c r="B133" s="66"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4903,8 +4903,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="24"/>
-      <c r="B134" s="31"/>
+      <c r="A134" s="68"/>
+      <c r="B134" s="66"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4916,12 +4916,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="24"/>
-      <c r="B135" s="31"/>
+      <c r="A135" s="68"/>
+      <c r="B135" s="66"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="24"/>
-      <c r="B136" s="34" t="s">
+      <c r="A136" s="68"/>
+      <c r="B136" s="65" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4936,8 +4936,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="24"/>
-      <c r="B137" s="31"/>
+      <c r="A137" s="68"/>
+      <c r="B137" s="66"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4949,8 +4949,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="24"/>
-      <c r="B138" s="31"/>
+      <c r="A138" s="68"/>
+      <c r="B138" s="66"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4962,8 +4962,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="24"/>
-      <c r="B139" s="31"/>
+      <c r="A139" s="68"/>
+      <c r="B139" s="66"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4975,8 +4975,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="24"/>
-      <c r="B140" s="31"/>
+      <c r="A140" s="68"/>
+      <c r="B140" s="66"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4988,12 +4988,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="24"/>
-      <c r="B141" s="31"/>
+      <c r="A141" s="68"/>
+      <c r="B141" s="66"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="24"/>
-      <c r="B142" s="34" t="s">
+      <c r="A142" s="68"/>
+      <c r="B142" s="65" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -5008,8 +5008,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="24"/>
-      <c r="B143" s="31"/>
+      <c r="A143" s="68"/>
+      <c r="B143" s="66"/>
       <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
@@ -5022,6 +5022,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5038,14 +5046,6 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Brownfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Brownfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B3F404-4EE8-465D-85FE-0A98AA77E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266CC73F-25CB-4F2E-A960-45EC38BDF82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,10 +1289,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1424,144 +1424,83 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1900,1197 +1839,1197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="9">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="28" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="10">
         <v>50</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="53"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="28" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="30">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="28" t="s">
+      <c r="E4" s="11">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="53"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="28" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="12">
         <v>0.03</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="53"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="28" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="13">
         <v>20</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="53"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="28" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="12">
         <v>0.08</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="53"/>
-      <c r="B8" s="63" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="43" t="s">
         <v>331</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="15">
         <f>0.36</f>
         <v>0.36</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="14" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="53"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="28" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="10">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="53"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="28" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="10">
         <v>7700</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="10" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="53"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="28" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="12">
         <v>0.05</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="28" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="10">
         <v>0.46</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="28" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="10">
         <v>2.54</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="7" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="53"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="28" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="13">
         <v>20</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="17">
         <v>0.06</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="53"/>
-      <c r="B16" s="63" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="18">
         <v>3.7</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="28" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="12">
         <v>0.27</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="7" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="28" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="12">
         <v>700</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="7" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="28" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="12">
         <v>0.02</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="53"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="28" t="s">
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="12">
         <v>20</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="53"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="34" t="s">
+      <c r="A21" s="33"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="17">
         <v>0.05</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
-      <c r="B22" s="56" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="10">
         <v>0.5</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="7" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="28" t="s">
+      <c r="A23" s="33"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="10">
         <v>1.75</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="7" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="28" t="s">
+      <c r="A24" s="33"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="10">
         <v>7000</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="7" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="28" t="s">
+      <c r="A25" s="33"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="12">
         <v>0.05</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="28" t="s">
+      <c r="A26" s="33"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="13">
         <v>15</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="53"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="28" t="s">
+      <c r="A27" s="33"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="52" t="s">
+      <c r="A28" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="19">
         <v>490</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="53"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="28" t="s">
+      <c r="A29" s="33"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="12">
         <v>0.01</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="53"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="28" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="13">
         <v>20</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="53"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="28" t="s">
+      <c r="A31" s="33"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="23">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="53"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="28" t="s">
+      <c r="A32" s="33"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="12">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="53"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="28" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="12">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="53"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="12">
         <v>0.05</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="53"/>
-      <c r="B35" s="57"/>
-      <c r="C35" s="34" t="s">
+      <c r="A35" s="33"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="34" t="s">
+      <c r="D35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="17">
         <v>0</v>
       </c>
-      <c r="F35" s="34" t="s">
+      <c r="F35" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="53"/>
-      <c r="B36" s="58" t="s">
+      <c r="A36" s="33"/>
+      <c r="B36" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="19">
         <v>2.83</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F36" s="8" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="53"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="28" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="12">
         <v>0.03</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="53"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="28" t="s">
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="13">
         <v>30</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="53"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="28" t="s">
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="12">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="53"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="28" t="s">
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="12">
         <v>0.98</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="53"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="28" t="s">
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="12">
         <v>0.98</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="53"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="28" t="s">
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="12">
         <v>0.05</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="53"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="34" t="s">
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="E43" s="35">
+      <c r="E43" s="17">
         <v>0</v>
       </c>
-      <c r="F43" s="34" t="s">
+      <c r="F43" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="53"/>
-      <c r="B44" s="58" t="s">
+      <c r="A44" s="33"/>
+      <c r="B44" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="33" t="s">
+      <c r="D44" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="18">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="14" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="53"/>
-      <c r="B45" s="60"/>
-      <c r="C45" s="28" t="s">
+      <c r="A45" s="33"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="10">
         <f>E46*4</f>
         <v>424</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="53"/>
-      <c r="B46" s="60"/>
-      <c r="C46" s="28" t="s">
+      <c r="A46" s="33"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="D46" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="10">
         <v>106</v>
       </c>
-      <c r="F46" s="28" t="s">
+      <c r="F46" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="53"/>
-      <c r="B47" s="60"/>
-      <c r="C47" s="28" t="s">
+      <c r="A47" s="33"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="28" t="s">
+      <c r="D47" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F47" s="28" t="s">
+      <c r="F47" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="53"/>
-      <c r="B48" s="60"/>
-      <c r="C48" s="28" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="D48" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="12">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="53"/>
-      <c r="B49" s="60"/>
-      <c r="C49" s="28" t="s">
+      <c r="A49" s="33"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="12">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="53"/>
-      <c r="B50" s="60"/>
-      <c r="C50" s="28" t="s">
+      <c r="A50" s="33"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="10">
         <v>0.25</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="53"/>
-      <c r="B51" s="60"/>
-      <c r="C51" s="28" t="s">
+      <c r="A51" s="33"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="28" t="s">
+      <c r="D51" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="12">
         <v>0</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="53"/>
-      <c r="B52" s="60"/>
-      <c r="C52" s="28" t="s">
+      <c r="A52" s="33"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="28" t="s">
+      <c r="D52" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="13">
         <v>15</v>
       </c>
-      <c r="F52" s="28" t="s">
+      <c r="F52" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="54"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="39" t="s">
+      <c r="A53" s="34"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="39" t="s">
+      <c r="D53" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="40">
+      <c r="E53" s="21">
         <v>0.1</v>
       </c>
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="52" t="s">
+      <c r="A54" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="D54" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="42">
+      <c r="E54" s="25">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="F54" s="26" t="s">
+      <c r="F54" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="53"/>
-      <c r="B55" s="58" t="s">
+      <c r="A55" s="33"/>
+      <c r="B55" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="33" t="s">
+      <c r="D55" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="18">
         <v>0.99</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="F55" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="53"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="28" t="s">
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="28" t="s">
+      <c r="D56" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="1">
         <v>1100</v>
       </c>
-      <c r="F56" s="28" t="s">
+      <c r="F56" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="53"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="28" t="s">
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="7" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="1">
         <v>17.84</v>
       </c>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="53"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="28" t="s">
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D58" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="10">
         <v>0</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="53"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="28" t="s">
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="28" t="s">
+      <c r="D59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="13">
         <v>25</v>
       </c>
-      <c r="F59" s="28" t="s">
+      <c r="F59" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="53"/>
-      <c r="B60" s="56"/>
-      <c r="C60" s="28" t="s">
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="28" t="s">
+      <c r="D60" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="29">
+      <c r="E60" s="10">
         <v>1000000</v>
       </c>
-      <c r="F60" s="28" t="s">
+      <c r="F60" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="53"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="34" t="s">
+      <c r="A61" s="33"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="35">
+      <c r="E61" s="17">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F61" s="34" t="s">
+      <c r="F61" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="53"/>
-      <c r="B62" s="58" t="s">
+      <c r="A62" s="33"/>
+      <c r="B62" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="33" t="s">
+      <c r="C62" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="33" t="s">
+      <c r="D62" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="36">
+      <c r="E62" s="18">
         <v>0.997</v>
       </c>
-      <c r="F62" s="33" t="s">
+      <c r="F62" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="53"/>
-      <c r="B63" s="56"/>
-      <c r="C63" s="28" t="s">
+      <c r="A63" s="33"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="28" t="s">
+      <c r="D63" s="7" t="s">
         <v>48</v>
       </c>
       <c r="E63" s="1">
         <v>1080</v>
       </c>
-      <c r="F63" s="28" t="s">
+      <c r="F63" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="53"/>
-      <c r="B64" s="56"/>
-      <c r="C64" s="28" t="s">
+      <c r="A64" s="33"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E64" s="1">
         <v>12.68</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="F64" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="53"/>
-      <c r="B65" s="56"/>
-      <c r="C65" s="28" t="s">
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F65" s="28" t="s">
+      <c r="F65" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="53"/>
-      <c r="B66" s="56"/>
-      <c r="C66" s="28" t="s">
+      <c r="A66" s="33"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="13">
         <v>25</v>
       </c>
-      <c r="F66" s="28" t="s">
+      <c r="F66" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="53"/>
-      <c r="B67" s="56"/>
-      <c r="C67" s="28" t="s">
+      <c r="A67" s="33"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D67" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="43">
+      <c r="E67" s="22">
         <v>1000000</v>
       </c>
-      <c r="F67" s="28" t="s">
+      <c r="F67" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="54"/>
-      <c r="B68" s="59"/>
-      <c r="C68" s="39" t="s">
+      <c r="A68" s="34"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="39" t="s">
+      <c r="D68" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="40">
+      <c r="E68" s="21">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F68" s="39" t="s">
+      <c r="F68" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="52" t="s">
+      <c r="A69" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="44" t="s">
+      <c r="B69" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="45" t="s">
+      <c r="C69" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="46">
+      <c r="E69" s="28">
         <v>0</v>
       </c>
-      <c r="F69" s="45" t="s">
+      <c r="F69" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="53"/>
-      <c r="B70" s="47" t="s">
+      <c r="A70" s="33"/>
+      <c r="B70" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C70" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="12">
         <v>0</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" s="7" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="53"/>
-      <c r="B71" s="48" t="s">
+      <c r="A71" s="33"/>
+      <c r="B71" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="49" t="s">
+      <c r="C71" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="49" t="s">
+      <c r="D71" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="50">
+      <c r="E71" s="31">
         <v>-1.5</v>
       </c>
-      <c r="F71" s="49" t="s">
+      <c r="F71" s="30" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="54"/>
-      <c r="B72" s="24" t="s">
+      <c r="A72" s="34"/>
+      <c r="B72" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="39" t="s">
+      <c r="C72" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="D72" s="39" t="s">
+      <c r="D72" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="40">
+      <c r="E72" s="21">
         <v>-1.7</v>
       </c>
-      <c r="F72" s="39" t="s">
+      <c r="F72" s="20" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3151,10 +3090,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3169,8 +3108,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="68"/>
-      <c r="B3" s="66"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3183,8 +3122,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="68"/>
-      <c r="B4" s="66"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3197,8 +3136,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="68"/>
-      <c r="B5" s="66"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3211,8 +3150,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="66"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3225,8 +3164,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="68"/>
-      <c r="B7" s="66"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3239,8 +3178,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="68"/>
-      <c r="B8" s="66"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3253,8 +3192,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="68"/>
-      <c r="B9" s="66"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3267,8 +3206,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="68"/>
-      <c r="B10" s="66"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3281,13 +3220,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="66"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="40"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="68"/>
-      <c r="B12" s="65" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="43" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3302,8 +3241,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="68"/>
-      <c r="B13" s="66"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3316,8 +3255,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="68"/>
-      <c r="B14" s="66"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3330,8 +3269,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="68"/>
-      <c r="B15" s="66"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3344,8 +3283,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="68"/>
-      <c r="B16" s="66"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3358,8 +3297,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="68"/>
-      <c r="B17" s="66"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3372,8 +3311,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="68"/>
-      <c r="B18" s="66"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3386,8 +3325,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="68"/>
-      <c r="B19" s="66"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3400,8 +3339,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="68"/>
-      <c r="B20" s="66"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3414,8 +3353,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="68"/>
-      <c r="B21" s="66"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3428,16 +3367,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="68"/>
-      <c r="B22" s="70"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="68"/>
-      <c r="B23" s="65" t="s">
+      <c r="A23" s="33"/>
+      <c r="B23" s="43" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3452,8 +3391,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="68"/>
-      <c r="B24" s="66"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3466,8 +3405,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="68"/>
-      <c r="B25" s="66"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3480,8 +3419,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="68"/>
-      <c r="B26" s="66"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3494,8 +3433,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="68"/>
-      <c r="B27" s="66"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="40"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3508,8 +3447,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="68"/>
-      <c r="B28" s="66"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3522,8 +3461,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="68"/>
-      <c r="B29" s="66"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3536,8 +3475,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="68"/>
-      <c r="B30" s="66"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3550,8 +3489,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="68"/>
-      <c r="B31" s="66"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="40"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3564,16 +3503,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="68"/>
-      <c r="B32" s="70"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="68"/>
-      <c r="B33" s="71" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="36" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3588,8 +3527,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="68"/>
-      <c r="B34" s="71"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3602,8 +3541,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="68"/>
-      <c r="B35" s="71"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3616,8 +3555,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="68"/>
-      <c r="B36" s="71"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3630,8 +3569,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="68"/>
-      <c r="B37" s="71"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3644,8 +3583,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="68"/>
-      <c r="B38" s="71"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3658,8 +3597,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="68"/>
-      <c r="B39" s="71"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3672,8 +3611,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="68"/>
-      <c r="B40" s="71"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3686,8 +3625,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="68"/>
-      <c r="B41" s="71"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3700,8 +3639,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="68"/>
-      <c r="B42" s="71"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3714,15 +3653,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="68"/>
-      <c r="B43" s="71"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="67" t="s">
+      <c r="A44" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="75" t="s">
+      <c r="B44" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3737,8 +3676,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="68"/>
-      <c r="B45" s="71"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3751,8 +3690,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="68"/>
-      <c r="B46" s="71"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3765,8 +3704,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="68"/>
-      <c r="B47" s="71"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3779,8 +3718,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="68"/>
-      <c r="B48" s="71"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3793,8 +3732,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="68"/>
-      <c r="B49" s="71"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3807,8 +3746,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="68"/>
-      <c r="B50" s="71"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3821,8 +3760,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="68"/>
-      <c r="B51" s="71"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3835,8 +3774,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="68"/>
-      <c r="B52" s="71"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3849,16 +3788,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="68"/>
-      <c r="B53" s="76"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="68"/>
-      <c r="B54" s="71" t="s">
+      <c r="A54" s="33"/>
+      <c r="B54" s="36" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3873,8 +3812,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="68"/>
-      <c r="B55" s="71"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="36"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3887,8 +3826,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="68"/>
-      <c r="B56" s="71"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3901,8 +3840,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="68"/>
-      <c r="B57" s="71"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3915,8 +3854,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="68"/>
-      <c r="B58" s="71"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3929,8 +3868,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="68"/>
-      <c r="B59" s="71"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3943,8 +3882,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="68"/>
-      <c r="B60" s="71"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3957,8 +3896,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="68"/>
-      <c r="B61" s="71"/>
+      <c r="A61" s="33"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3971,8 +3910,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="68"/>
-      <c r="B62" s="71"/>
+      <c r="A62" s="33"/>
+      <c r="B62" s="36"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3985,13 +3924,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="68"/>
-      <c r="B63" s="76"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="37"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="68"/>
-      <c r="B64" s="73" t="s">
+      <c r="A64" s="33"/>
+      <c r="B64" s="38" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -4006,8 +3945,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="68"/>
-      <c r="B65" s="71"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -4020,8 +3959,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="68"/>
-      <c r="B66" s="66"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="40"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -4034,8 +3973,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="68"/>
-      <c r="B67" s="66"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="40"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -4048,8 +3987,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="68"/>
-      <c r="B68" s="66"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="40"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4062,8 +4001,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="68"/>
-      <c r="B69" s="66"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="40"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4076,8 +4015,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="68"/>
-      <c r="B70" s="66"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="40"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4090,8 +4029,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="68"/>
-      <c r="B71" s="66"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="40"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4104,8 +4043,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="68"/>
-      <c r="B72" s="66"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4118,8 +4057,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="68"/>
-      <c r="B73" s="66"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="40"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4132,8 +4071,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="68"/>
-      <c r="B74" s="66"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4146,18 +4085,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="72"/>
-      <c r="B75" s="74"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="41"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="21"/>
       <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="67" t="s">
+      <c r="A76" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="69" t="s">
+      <c r="B76" s="42" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4172,8 +4111,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="68"/>
-      <c r="B77" s="66"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="40"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4186,13 +4125,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="68"/>
-      <c r="B78" s="70"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="44"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="68"/>
-      <c r="B79" s="73" t="s">
+      <c r="A79" s="33"/>
+      <c r="B79" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4207,8 +4146,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="68"/>
-      <c r="B80" s="71"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4221,8 +4160,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="68"/>
-      <c r="B81" s="71"/>
+      <c r="A81" s="33"/>
+      <c r="B81" s="36"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4235,8 +4174,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="68"/>
-      <c r="B82" s="71"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4249,8 +4188,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="68"/>
-      <c r="B83" s="71"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="36"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4263,8 +4202,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="68"/>
-      <c r="B84" s="71"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="36"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4277,8 +4216,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="68"/>
-      <c r="B85" s="71"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4291,8 +4230,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="68"/>
-      <c r="B86" s="71"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4305,8 +4244,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="68"/>
-      <c r="B87" s="71"/>
+      <c r="A87" s="33"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4319,12 +4258,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="68"/>
-      <c r="B88" s="76"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="37"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="68"/>
-      <c r="B89" s="73" t="s">
+      <c r="A89" s="33"/>
+      <c r="B89" s="38" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4339,8 +4278,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="68"/>
-      <c r="B90" s="71"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="36"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4353,8 +4292,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="68"/>
-      <c r="B91" s="71"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="36"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4367,8 +4306,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="68"/>
-      <c r="B92" s="71"/>
+      <c r="A92" s="33"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4381,8 +4320,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="68"/>
-      <c r="B93" s="71"/>
+      <c r="A93" s="33"/>
+      <c r="B93" s="36"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4395,8 +4334,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="68"/>
-      <c r="B94" s="71"/>
+      <c r="A94" s="33"/>
+      <c r="B94" s="36"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4409,8 +4348,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="68"/>
-      <c r="B95" s="71"/>
+      <c r="A95" s="33"/>
+      <c r="B95" s="36"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4423,8 +4362,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="68"/>
-      <c r="B96" s="71"/>
+      <c r="A96" s="33"/>
+      <c r="B96" s="36"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4437,8 +4376,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="68"/>
-      <c r="B97" s="71"/>
+      <c r="A97" s="33"/>
+      <c r="B97" s="36"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4451,14 +4390,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="72"/>
-      <c r="B98" s="77"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="39"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="67" t="s">
+      <c r="A99" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="69" t="s">
+      <c r="B99" s="42" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4473,8 +4412,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="68"/>
-      <c r="B100" s="66"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="40"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4487,8 +4426,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="68"/>
-      <c r="B101" s="66"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="40"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4501,16 +4440,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="68"/>
-      <c r="B102" s="70"/>
+      <c r="A102" s="33"/>
+      <c r="B102" s="44"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="68"/>
-      <c r="B103" s="65" t="s">
+      <c r="A103" s="33"/>
+      <c r="B103" s="43" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4525,8 +4464,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="68"/>
-      <c r="B104" s="66"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="40"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4539,8 +4478,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="68"/>
-      <c r="B105" s="66"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="40"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4553,13 +4492,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="68"/>
-      <c r="B106" s="70"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="44"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="68"/>
-      <c r="B107" s="65" t="s">
+      <c r="A107" s="33"/>
+      <c r="B107" s="43" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4574,8 +4513,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="68"/>
-      <c r="B108" s="66"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="40"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4588,16 +4527,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="68"/>
-      <c r="B109" s="70"/>
+      <c r="A109" s="33"/>
+      <c r="B109" s="44"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="68"/>
-      <c r="B110" s="65" t="s">
+      <c r="A110" s="33"/>
+      <c r="B110" s="43" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4612,8 +4551,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="68"/>
-      <c r="B111" s="66"/>
+      <c r="A111" s="33"/>
+      <c r="B111" s="40"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4626,18 +4565,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="72"/>
-      <c r="B112" s="74"/>
+      <c r="A112" s="34"/>
+      <c r="B112" s="41"/>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="21"/>
       <c r="F112" s="20"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="67" t="s">
+      <c r="A113" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="69" t="s">
+      <c r="B113" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4652,8 +4591,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="68"/>
-      <c r="B114" s="66"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="40"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4665,16 +4604,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="68"/>
-      <c r="B115" s="70"/>
+      <c r="A115" s="33"/>
+      <c r="B115" s="44"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="68"/>
-      <c r="B116" s="65" t="s">
+      <c r="A116" s="33"/>
+      <c r="B116" s="43" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4688,8 +4627,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="68"/>
-      <c r="B117" s="66"/>
+      <c r="A117" s="33"/>
+      <c r="B117" s="40"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4701,8 +4640,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="68"/>
-      <c r="B118" s="66"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="40"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4714,8 +4653,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="68"/>
-      <c r="B119" s="66"/>
+      <c r="A119" s="33"/>
+      <c r="B119" s="40"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4727,8 +4666,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="68"/>
-      <c r="B120" s="66"/>
+      <c r="A120" s="33"/>
+      <c r="B120" s="40"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4740,8 +4679,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="68"/>
-      <c r="B121" s="66"/>
+      <c r="A121" s="33"/>
+      <c r="B121" s="40"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4753,12 +4692,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="68"/>
-      <c r="B122" s="66"/>
+      <c r="A122" s="33"/>
+      <c r="B122" s="40"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="68"/>
-      <c r="B123" s="65" t="s">
+      <c r="A123" s="33"/>
+      <c r="B123" s="43" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4773,8 +4712,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="68"/>
-      <c r="B124" s="66"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="40"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4786,8 +4725,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="68"/>
-      <c r="B125" s="66"/>
+      <c r="A125" s="33"/>
+      <c r="B125" s="40"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4799,8 +4738,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="68"/>
-      <c r="B126" s="66"/>
+      <c r="A126" s="33"/>
+      <c r="B126" s="40"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4812,8 +4751,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="68"/>
-      <c r="B127" s="66"/>
+      <c r="A127" s="33"/>
+      <c r="B127" s="40"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4825,8 +4764,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="68"/>
-      <c r="B128" s="66"/>
+      <c r="A128" s="33"/>
+      <c r="B128" s="40"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4838,8 +4777,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="68"/>
-      <c r="B129" s="66"/>
+      <c r="A129" s="33"/>
+      <c r="B129" s="40"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4851,8 +4790,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="68"/>
-      <c r="B130" s="66"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="40"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4864,8 +4803,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="68"/>
-      <c r="B131" s="66"/>
+      <c r="A131" s="33"/>
+      <c r="B131" s="40"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4877,8 +4816,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="68"/>
-      <c r="B132" s="66"/>
+      <c r="A132" s="33"/>
+      <c r="B132" s="40"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4890,8 +4829,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="68"/>
-      <c r="B133" s="66"/>
+      <c r="A133" s="33"/>
+      <c r="B133" s="40"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4903,8 +4842,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="68"/>
-      <c r="B134" s="66"/>
+      <c r="A134" s="33"/>
+      <c r="B134" s="40"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4916,12 +4855,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="68"/>
-      <c r="B135" s="66"/>
+      <c r="A135" s="33"/>
+      <c r="B135" s="40"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="68"/>
-      <c r="B136" s="65" t="s">
+      <c r="A136" s="33"/>
+      <c r="B136" s="43" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4936,8 +4875,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="68"/>
-      <c r="B137" s="66"/>
+      <c r="A137" s="33"/>
+      <c r="B137" s="40"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4949,8 +4888,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="68"/>
-      <c r="B138" s="66"/>
+      <c r="A138" s="33"/>
+      <c r="B138" s="40"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4962,8 +4901,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="68"/>
-      <c r="B139" s="66"/>
+      <c r="A139" s="33"/>
+      <c r="B139" s="40"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4975,8 +4914,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="68"/>
-      <c r="B140" s="66"/>
+      <c r="A140" s="33"/>
+      <c r="B140" s="40"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4988,12 +4927,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="68"/>
-      <c r="B141" s="66"/>
+      <c r="A141" s="33"/>
+      <c r="B141" s="40"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="68"/>
-      <c r="B142" s="65" t="s">
+      <c r="A142" s="33"/>
+      <c r="B142" s="43" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -5008,8 +4947,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="68"/>
-      <c r="B143" s="66"/>
+      <c r="A143" s="33"/>
+      <c r="B143" s="40"/>
       <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
@@ -5022,14 +4961,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5046,6 +4977,14 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
